--- a/AAII_Financials/Quarterly/PSO_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PSO_QTR_FIN.xlsx
@@ -656,27 +656,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AC102"/>
+  <dimension ref="A5:AE102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
@@ -684,352 +684,378 @@
     <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9.140625" style="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>43281</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>43100</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42916</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42735</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42551</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42369</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AD7" s="2">
         <v>42185</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AE7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1180200</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1174600</v>
+      </c>
+      <c r="F8" s="3">
         <v>1248300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>1246700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>1179600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>1112400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>1125500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>1204900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>1108300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>1107600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>1143200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>1095200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>1193900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>1162300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>1236800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>2437700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>1851000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>2531200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>2181100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>2761900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>2482500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>3489700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>2725400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>3308100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>2412400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>3223000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AD8" s="3">
         <v>2629600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AE8" s="3">
         <v>3282800</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>576500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>573700</v>
+      </c>
+      <c r="F9" s="3">
         <v>588200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>587400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>577500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>544600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>542100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>580400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>552900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>552600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>559800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>536300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>610000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>593800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>652400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1176000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1052000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1183700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>1078000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1257700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1214000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1518400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>1322100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>1454500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>1179000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>1322600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AD9" s="3">
         <v>1273300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AE9" s="3">
         <v>1370800</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>603700</v>
+      </c>
+      <c r="E10" s="3">
+        <v>600800</v>
+      </c>
+      <c r="F10" s="3">
         <v>660200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>659300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>602100</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>567800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>583400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>624600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>555400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>555100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>583400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>558900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>583900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>568500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>584400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>1261700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>798900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>1347500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>1103100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>1504100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>1268500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>1971200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>1403300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>1853600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>1233300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>1900400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AD10" s="3">
         <v>1356300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AE10" s="3">
         <v>1912000</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1059,55 +1085,57 @@
       <c r="AA11" s="3"/>
       <c r="AB11" s="3"/>
       <c r="AC11" s="3"/>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD11" s="3"/>
+      <c r="AE11" s="3"/>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>86900</v>
+      </c>
+      <c r="E12" s="3">
+        <v>86500</v>
+      </c>
+      <c r="F12" s="3">
         <v>151400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="G12" s="3">
         <v>151200</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>95200</v>
       </c>
-      <c r="G12" s="3">
+      <c r="I12" s="3">
         <v>89800</v>
       </c>
-      <c r="H12" s="3">
+      <c r="J12" s="3">
         <v>92000</v>
       </c>
-      <c r="I12" s="3">
+      <c r="K12" s="3">
         <v>98500</v>
       </c>
-      <c r="J12" s="3">
+      <c r="L12" s="3">
         <v>91000</v>
       </c>
-      <c r="K12" s="3">
+      <c r="M12" s="3">
         <v>90900</v>
       </c>
-      <c r="L12" s="3">
+      <c r="N12" s="3">
         <v>93600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="O12" s="3">
         <v>89700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="P12" s="3">
         <v>87000</v>
       </c>
-      <c r="O12" s="3">
+      <c r="Q12" s="3">
         <v>84700</v>
       </c>
-      <c r="P12" s="3">
+      <c r="R12" s="3">
         <v>100600</v>
-      </c>
-      <c r="Q12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S12" s="3" t="s">
         <v>8</v>
@@ -1142,8 +1170,14 @@
       <c r="AC12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1225,139 +1259,151 @@
       <c r="AC13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>-10800</v>
+        <v>15300</v>
       </c>
       <c r="E14" s="3">
-        <v>-10800</v>
+        <v>15200</v>
       </c>
       <c r="F14" s="3">
-        <v>-2100</v>
+        <v>-15500</v>
       </c>
       <c r="G14" s="3">
+        <v>-15500</v>
+      </c>
+      <c r="H14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="I14" s="3">
+        <v>2600</v>
+      </c>
+      <c r="J14" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K14" s="3">
+        <v>2700</v>
+      </c>
+      <c r="L14" s="3">
+        <v>8800</v>
+      </c>
+      <c r="M14" s="3">
+        <v>8800</v>
+      </c>
+      <c r="N14" s="3">
         <v>-1900</v>
       </c>
-      <c r="H14" s="3">
-        <v>2500</v>
-      </c>
-      <c r="I14" s="3">
-        <v>2700</v>
-      </c>
-      <c r="J14" s="3">
-        <v>8800</v>
-      </c>
-      <c r="K14" s="3">
-        <v>8800</v>
-      </c>
-      <c r="L14" s="3">
-        <v>-1900</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="O14" s="3">
         <v>-1800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>1300</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>1200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>89200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>3800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-224500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>-12400</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>-7200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-28100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-275500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>-181100</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>3138100</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>1107400</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>101400</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>38500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>38300</v>
+      </c>
+      <c r="F15" s="3">
         <v>22200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>22200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>32900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>31000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>13800</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>14700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>37900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>37900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>15300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>14600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>39400</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>38400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>18700</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
       <c r="S15" s="3">
         <v>0</v>
       </c>
@@ -1391,8 +1437,14 @@
       <c r="AC15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+      <c r="AD15" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1419,174 +1471,188 @@
       <c r="AA16" s="3"/>
       <c r="AB16" s="3"/>
       <c r="AC16" s="3"/>
-    </row>
-    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD16" s="3"/>
+      <c r="AE16" s="3"/>
+    </row>
+    <row r="17" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1074000</v>
+        <v>1023000</v>
       </c>
       <c r="E17" s="3">
-        <v>1072700</v>
+        <v>1018100</v>
       </c>
       <c r="F17" s="3">
-        <v>1011100</v>
+        <v>1062600</v>
       </c>
       <c r="G17" s="3">
-        <v>953500</v>
+        <v>1061200</v>
       </c>
       <c r="H17" s="3">
-        <v>918300</v>
+        <v>1022700</v>
       </c>
       <c r="I17" s="3">
+        <v>964500</v>
+      </c>
+      <c r="J17" s="3">
+        <v>900800</v>
+      </c>
+      <c r="K17" s="3">
         <v>983100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>959200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>958600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>957900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>917700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1038900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>1011400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1058500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>2048700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>1718200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>2235900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>2137000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>2371500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>2172400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>2874100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>2704100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>6031100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>2782100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>3581600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AD17" s="3">
         <v>2799500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AE17" s="3">
         <v>2775800</v>
       </c>
     </row>
-    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>174300</v>
+        <v>157200</v>
       </c>
       <c r="E18" s="3">
-        <v>174100</v>
+        <v>156500</v>
       </c>
       <c r="F18" s="3">
-        <v>168500</v>
+        <v>185700</v>
       </c>
       <c r="G18" s="3">
-        <v>158900</v>
+        <v>185500</v>
       </c>
       <c r="H18" s="3">
-        <v>207200</v>
+        <v>156900</v>
       </c>
       <c r="I18" s="3">
+        <v>147900</v>
+      </c>
+      <c r="J18" s="3">
+        <v>224700</v>
+      </c>
+      <c r="K18" s="3">
         <v>221800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>149100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>149000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>185300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>177600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>155000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>150900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>178300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>389000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>132700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>295300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>44100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>390400</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>310100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>615600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>21300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>-2723100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>-369700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>-358700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AD18" s="3">
         <v>-169900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AE18" s="3">
         <v>507000</v>
       </c>
     </row>
-    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1616,8 +1682,10 @@
       <c r="AA19" s="3"/>
       <c r="AB19" s="3"/>
       <c r="AC19" s="3"/>
-    </row>
-    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD19" s="3"/>
+      <c r="AE19" s="3"/>
+    </row>
+    <row r="20" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1628,210 +1696,222 @@
         <v>1300</v>
       </c>
       <c r="F20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="G20" s="3">
+        <v>1300</v>
+      </c>
+      <c r="H20" s="3">
         <v>4800</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>4500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>3800</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>4000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-7600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-7600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>8900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>8500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-5100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-4900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-7800</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>52500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-89300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-23600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-28600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>-29300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>-41300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>-5700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>-34600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>-49300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>-25900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>-33900</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AD20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AE20" s="3">
         <v>-123800</v>
       </c>
     </row>
-    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>195200</v>
+        <v>194400</v>
       </c>
       <c r="E21" s="3">
-        <v>194900</v>
+        <v>193400</v>
       </c>
       <c r="F21" s="3">
-        <v>196600</v>
+        <v>206600</v>
       </c>
       <c r="G21" s="3">
-        <v>185400</v>
+        <v>206300</v>
       </c>
       <c r="H21" s="3">
-        <v>217200</v>
+        <v>185000</v>
       </c>
       <c r="I21" s="3">
+        <v>174400</v>
+      </c>
+      <c r="J21" s="3">
+        <v>234700</v>
+      </c>
+      <c r="K21" s="3">
         <v>232500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>194600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>194500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>191700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>183700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>199500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>194200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>204800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>636000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>248100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>477700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>203900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>519700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>432600</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>833500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>193100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>-2550600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>-157700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>954800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AD21" s="3">
         <v>46100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AE21" s="3">
         <v>722900</v>
       </c>
     </row>
-    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>31200</v>
+      </c>
+      <c r="E22" s="3">
+        <v>31000</v>
+      </c>
+      <c r="F22" s="3">
         <v>25600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>25500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>25300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>23900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>18800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>20100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>31000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>30900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>15900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>15300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>22900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>22300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>38000</v>
       </c>
-      <c r="Q22" s="3">
-        <v>0</v>
-      </c>
-      <c r="R22" s="3">
-        <v>0</v>
-      </c>
       <c r="S22" s="3">
         <v>0</v>
       </c>
@@ -1865,174 +1945,192 @@
       <c r="AC22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD22" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>136000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>135300</v>
+      </c>
+      <c r="F23" s="3">
         <v>160800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>160600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>149300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>140800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>186500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>199700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>134000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>133900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>163700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>156800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>150000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>146000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>83100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>441500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>43400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>271700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>15500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>361100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>268900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>609900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>-13300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>-2772300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>-395600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>-392600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AD23" s="3">
         <v>-173800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AE23" s="3">
         <v>383200</v>
       </c>
     </row>
-    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>37200</v>
+      </c>
+      <c r="E24" s="3">
+        <v>37000</v>
+      </c>
+      <c r="F24" s="3">
         <v>46400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>46400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>35600</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>33600</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>13100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>14100</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>34100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>34100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>40800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>39100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>31100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>30300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>18100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>80600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>-16100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>1200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-41700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>-128100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>17300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>17000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>8000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>-167500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>-111200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>-53500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AD24" s="3">
         <v>-52700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AE24" s="3">
         <v>86900</v>
       </c>
     </row>
-    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2114,174 +2212,192 @@
       <c r="AC25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>98800</v>
+      </c>
+      <c r="E26" s="3">
+        <v>98400</v>
+      </c>
+      <c r="F26" s="3">
         <v>114400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>114300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>113700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>107200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>173400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>185600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>99800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>99800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>122900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>117800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>118800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>115700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>65100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>360900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>59500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>270500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>57200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>489200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>251600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>592900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>-21300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>-2604800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>-284400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>-339100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AD26" s="3">
         <v>-121100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AE26" s="3">
         <v>296300</v>
       </c>
     </row>
-    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E27" s="3">
+        <v>97700</v>
+      </c>
+      <c r="F27" s="3">
         <v>115100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>114900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>112300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>105900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>173400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>185600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>99200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>99100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>122300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>117200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>118200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>115100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>63900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>360900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>59500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>269300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>56000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>488000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>250200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>591500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>-2606100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>-285700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>-339100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AD27" s="3">
         <v>-121100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AE27" s="3">
         <v>297600</v>
       </c>
     </row>
-    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2363,8 +2479,14 @@
       <c r="AC28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2407,11 +2529,11 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2419,35 +2541,41 @@
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="V29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
         <v>7100</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC29" s="3">
         <v>1515600</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AD29" s="3">
         <v>17100</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AE29" s="3">
         <v>23700</v>
       </c>
     </row>
-    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2529,8 +2657,14 @@
       <c r="AC30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2612,8 +2746,14 @@
       <c r="AC31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2624,162 +2764,174 @@
         <v>-1300</v>
       </c>
       <c r="F32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="G32" s="3">
+        <v>-1300</v>
+      </c>
+      <c r="H32" s="3">
         <v>-4800</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-4500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-3800</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-4000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>7600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>7600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-8900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-8500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>5100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>4900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>7800</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-52500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>89300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>23600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>28600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>29300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>41300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>5700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>34600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>49300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>25900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>33900</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AD32" s="3">
         <v>4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AE32" s="3">
         <v>123800</v>
       </c>
     </row>
-    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E33" s="3">
+        <v>97700</v>
+      </c>
+      <c r="F33" s="3">
         <v>115100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>114900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>112300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>105900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>173400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>185600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>99200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>99100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>122300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>117200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>118200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>115100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>63900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>360900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>59500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>269300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>56000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>488000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>250200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>598600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>-2606100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>-285700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1176500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AD33" s="3">
         <v>-104000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AE33" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2861,179 +3013,197 @@
       <c r="AC34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E35" s="3">
+        <v>97700</v>
+      </c>
+      <c r="F35" s="3">
         <v>115100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>114900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>112300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>105900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>173400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>185600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>99200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>99100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>122300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>117200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>118200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>115100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>63900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>360900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>59500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>269300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>56000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>488000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>250200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>598600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>-2606100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>-285700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1176500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AD35" s="3">
         <v>-104000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AE35" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>43281</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>43100</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42916</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42735</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42551</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42369</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AD38" s="2">
         <v>42185</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AE38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3063,8 +3233,10 @@
       <c r="AA39" s="3"/>
       <c r="AB39" s="3"/>
       <c r="AC39" s="3"/>
-    </row>
-    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD39" s="3"/>
+      <c r="AE39" s="3"/>
+    </row>
+    <row r="40" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3094,91 +3266,99 @@
       <c r="AA40" s="3"/>
       <c r="AB40" s="3"/>
       <c r="AC40" s="3"/>
-    </row>
-    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD40" s="3"/>
+      <c r="AE40" s="3"/>
+    </row>
+    <row r="41" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>448200</v>
+        <v>449800</v>
       </c>
       <c r="E41" s="3">
         <v>447600</v>
       </c>
       <c r="F41" s="3">
+        <v>448200</v>
+      </c>
+      <c r="G41" s="3">
+        <v>447600</v>
+      </c>
+      <c r="H41" s="3">
         <v>475400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>448300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>679800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>727800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>419600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>419300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>397400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>380700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>451100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>439200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>672300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>1403700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>852300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>542200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>497300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>692900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>439300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>733000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>609800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>1796900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>1267000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>2221200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AD41" s="3">
         <v>475400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AE41" s="3">
         <v>697900</v>
       </c>
     </row>
-    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3240,609 +3420,657 @@
         <v>0</v>
       </c>
       <c r="W42" s="3">
+        <v>0</v>
+      </c>
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
         <v>11300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Z42" s="3">
         <v>14600</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="AA42" s="3">
         <v>12300</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AB42" s="3">
         <v>40100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AC42" s="3">
         <v>36500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AD42" s="3">
         <v>34200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AE42" s="3">
         <v>21100</v>
       </c>
     </row>
-    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1363900</v>
+      </c>
+      <c r="E43" s="3">
+        <v>1357400</v>
+      </c>
+      <c r="F43" s="3">
         <v>1040400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>1039100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>1387900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>1308800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>999000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>1069600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>1395200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>1394300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>926000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>887200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>1359700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>1323700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>1141000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>1430600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>1348500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>1582000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>1518100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>1437000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>1409600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>1570800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>1642900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>1671300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AB43" s="3">
         <v>1736200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AC43" s="3">
         <v>1674700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AD43" s="3">
         <v>1677600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AE43" s="3">
         <v>1725000</v>
       </c>
     </row>
-    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>95500</v>
+      </c>
+      <c r="E44" s="3">
+        <v>95100</v>
+      </c>
+      <c r="F44" s="3">
         <v>88800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="G44" s="3">
         <v>88700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="H44" s="3">
         <v>97300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="I44" s="3">
         <v>91700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="J44" s="3">
         <v>92600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="K44" s="3">
         <v>99200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="L44" s="3">
         <v>112500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="M44" s="3">
         <v>112400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="N44" s="3">
         <v>115900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="O44" s="3">
         <v>111000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="P44" s="3">
         <v>139800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="Q44" s="3">
         <v>136100</v>
       </c>
-      <c r="P44" s="3">
+      <c r="R44" s="3">
         <v>126500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="S44" s="3">
         <v>165100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="T44" s="3">
         <v>215900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="U44" s="3">
         <v>209700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="V44" s="3">
         <v>252800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="W44" s="3">
         <v>200100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="X44" s="3">
         <v>222300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="Y44" s="3">
         <v>209400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Z44" s="3">
         <v>316900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="AA44" s="3">
         <v>289400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AB44" s="3">
         <v>354200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AC44" s="3">
         <v>275200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AD44" s="3">
         <v>330500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AE44" s="3">
         <v>295000</v>
       </c>
     </row>
-    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1114500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>1109200</v>
+      </c>
+      <c r="F45" s="3">
         <v>1109000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>1107600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>1248100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>1177000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>1224400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>1310800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>1258700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>1257900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>1229200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>1177600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>1244100</v>
       </c>
-      <c r="O45" s="3">
+      <c r="Q45" s="3">
         <v>1211200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="R45" s="3">
         <v>1214500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="S45" s="3">
         <v>1181100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="T45" s="3">
         <v>1156200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="U45" s="3">
         <v>1110500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="V45" s="3">
         <v>996900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="W45" s="3">
         <v>997900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="X45" s="3">
         <v>1026300</v>
       </c>
-      <c r="W45" s="3">
+      <c r="Y45" s="3">
         <v>1048600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Z45" s="3">
         <v>1319400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="AA45" s="3">
         <v>1261200</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AB45" s="3">
         <v>1221700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AC45" s="3">
         <v>1138700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AD45" s="3">
         <v>1114000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AE45" s="3">
         <v>1111400</v>
       </c>
     </row>
-    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3023700</v>
+      </c>
+      <c r="E46" s="3">
+        <v>3009400</v>
+      </c>
+      <c r="F46" s="3">
         <v>3122500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>3118500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>3208700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>3025900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>3415300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>3656300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>3186000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>3184000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>3099000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>2969000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>3194800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="Q46" s="3">
         <v>3110200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="R46" s="3">
         <v>3395400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="S46" s="3">
         <v>4180500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="T46" s="3">
         <v>3572900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="U46" s="3">
         <v>3444500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="V46" s="3">
         <v>3265100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="W46" s="3">
         <v>3327900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="X46" s="3">
         <v>3097500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="Y46" s="3">
         <v>3573200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Z46" s="3">
         <v>3903700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="AA46" s="3">
         <v>5031100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AB46" s="3">
         <v>4619200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AC46" s="3">
         <v>5346400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AD46" s="3">
         <v>3631700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AE46" s="3">
         <v>3850300</v>
       </c>
     </row>
-    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>145900</v>
+      </c>
+      <c r="E47" s="3">
+        <v>145300</v>
+      </c>
+      <c r="F47" s="3">
         <v>179000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>178800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>187700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>177000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>191500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>205100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>192100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>192000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>210200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>201400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>197000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>191800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>190400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>469600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>559500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>548400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1152000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>713600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>764100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>817900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>1141000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>1743900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>1772400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>1775200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AD47" s="3">
         <v>1603900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AE47" s="3">
         <v>1651300</v>
       </c>
     </row>
-    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>293200</v>
+      </c>
+      <c r="E48" s="3">
+        <v>291800</v>
+      </c>
+      <c r="F48" s="3">
         <v>282600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>282300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>278100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>262300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>270400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>289500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>261600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>261400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>276400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>264800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>287200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>279600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>301200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>659000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>790300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>766800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>765600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>289100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>356700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>397600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>407400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>422400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>438300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>417400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AD48" s="3">
         <v>417400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AE48" s="3">
         <v>439800</v>
       </c>
     </row>
-    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4005600</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3986500</v>
+      </c>
+      <c r="F49" s="3">
         <v>4049800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4044700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3848500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3629200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3788300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4055800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>3854600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>3852100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3937200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3772000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3972500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3867300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3827900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>3508700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3731700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3598300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3651500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>3670700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>4082500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>4194400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>4348400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>4239200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>7260400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>6735500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AD49" s="3">
         <v>7816500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AE49" s="3">
         <v>8308900</v>
       </c>
     </row>
-    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3924,8 +4152,14 @@
       <c r="AC50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4007,91 +4241,103 @@
       <c r="AC51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>814600</v>
+      </c>
+      <c r="E52" s="3">
+        <v>810800</v>
+      </c>
+      <c r="F52" s="3">
         <v>905800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>904600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>791900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>746800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>806200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>863200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>772200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>771700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>895500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>857900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>884500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>861000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>912100</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>716600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>671200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>1134100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>664200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>1642000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>1863500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>2179300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>1978500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>960600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>1199700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>901300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AD52" s="3">
         <v>886200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AE52" s="3">
         <v>757200</v>
       </c>
     </row>
-    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4173,91 +4419,103 @@
       <c r="AC53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>8455600</v>
+      </c>
+      <c r="E54" s="3">
+        <v>8415400</v>
+      </c>
+      <c r="F54" s="3">
         <v>8691800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>8680800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>8528600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>8042700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>8628300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>9237400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>8478800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>8473300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>8568600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>8209100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>8745600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>8514000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>8824600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>9534400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>9325600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>9492100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>9498300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>9643300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>10164300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>11162400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>11778900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>12397300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>15290100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>15175600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AD54" s="3">
         <v>14355600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AE54" s="3">
         <v>15007500</v>
       </c>
     </row>
-    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4287,8 +4545,10 @@
       <c r="AA55" s="3"/>
       <c r="AB55" s="3"/>
       <c r="AC55" s="3"/>
-    </row>
-    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD55" s="3"/>
+      <c r="AE55" s="3"/>
+    </row>
+    <row r="56" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4318,506 +4578,544 @@
       <c r="AA56" s="3"/>
       <c r="AB56" s="3"/>
       <c r="AC56" s="3"/>
-    </row>
-    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD56" s="3"/>
+      <c r="AE56" s="3"/>
+    </row>
+    <row r="57" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1362600</v>
+      </c>
+      <c r="E57" s="3">
+        <v>1356100</v>
+      </c>
+      <c r="F57" s="3">
         <v>378200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>377700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1235800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1165400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>341800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>365900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1309300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1308400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>403800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>386800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1296200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>1261900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>419300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>1530400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>1300100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>1585700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>1441700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="W57" s="3">
         <v>1707900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="X57" s="3">
         <v>1561400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="Y57" s="3">
         <v>1899100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Z57" s="3">
         <v>1772100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="AA57" s="3">
         <v>2006300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AB57" s="3">
         <v>1891400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AC57" s="3">
         <v>1813000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AD57" s="3">
         <v>1721000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AE57" s="3">
         <v>2108200</v>
       </c>
     </row>
-    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E58" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F58" s="3">
         <v>84800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>84700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>100000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>94300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>462000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>494600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>451200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>450900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>91700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>87900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>101700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>99000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>116900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>325000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>362300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>114200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="V58" s="3">
         <v>168100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="W58" s="3">
         <v>56100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="X58" s="3">
         <v>43900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="Y58" s="3">
         <v>26900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Z58" s="3">
         <v>354200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="AA58" s="3">
         <v>54200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AB58" s="3">
         <v>148700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AC58" s="3">
         <v>367800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AD58" s="3">
         <v>965200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AE58" s="3">
         <v>450300</v>
       </c>
     </row>
-    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>54400</v>
+      </c>
+      <c r="E59" s="3">
+        <v>54100</v>
+      </c>
+      <c r="F59" s="3">
         <v>541000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>540400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>52100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>49100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>514500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>550900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>31600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>31600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>487800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>467400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>81300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>79200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>627700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>154800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>178600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>151400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>64400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>140300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>374000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>362300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>279600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>309100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>181000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>306500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AD59" s="3">
         <v>221200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AE59" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1511200</v>
+      </c>
+      <c r="E60" s="3">
+        <v>1504000</v>
+      </c>
+      <c r="F60" s="3">
         <v>1562600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>1560600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>1387900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>1308800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>1850300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>1981000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>1792100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>1790900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>1788400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>1713300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>1479200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="Q60" s="3">
         <v>1440000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="R60" s="3">
         <v>1782000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="S60" s="3">
         <v>2010300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="T60" s="3">
         <v>1841100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="U60" s="3">
         <v>1851300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="V60" s="3">
         <v>1674300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="W60" s="3">
         <v>1904300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="X60" s="3">
         <v>1979300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="Y60" s="3">
         <v>2288200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Z60" s="3">
         <v>2405800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="AA60" s="3">
         <v>2369600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AB60" s="3">
         <v>2221000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AC60" s="3">
         <v>2487300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AD60" s="3">
         <v>2907500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AE60" s="3">
         <v>2879800</v>
       </c>
     </row>
-    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2242300</v>
+      </c>
+      <c r="E61" s="3">
+        <v>2231600</v>
+      </c>
+      <c r="F61" s="3">
         <v>1912500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>1910100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>1957800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>1846300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>1453500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>1556100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>1646700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>1645700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>1441900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>1381400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>1716800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>1671400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>1443500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>1787600</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>1922900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>1950500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>2228800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>822200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>1422900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>1508500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>2417800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>2985400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>3004500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>2671200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AD61" s="3">
         <v>2532200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AE61" s="3">
         <v>2479500</v>
       </c>
     </row>
-    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E62" s="3">
+        <v>93800</v>
+      </c>
+      <c r="F62" s="3">
         <v>36300</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>36300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>102800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>96900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>42600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>45600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>99800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>99800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>51000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>48800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>119500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>116300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>89200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>446600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>359800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>326300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>477000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>1396800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>1308500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>1675500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>1680200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>1687300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>1713000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>1646000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AD62" s="3">
         <v>1800100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AE62" s="3">
         <v>1767100</v>
       </c>
     </row>
-    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4899,8 +5197,14 @@
       <c r="AC63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4982,8 +5286,14 @@
       <c r="AC64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5065,91 +5375,103 @@
       <c r="AC65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3998900</v>
+      </c>
+      <c r="E66" s="3">
+        <v>3979900</v>
+      </c>
+      <c r="F66" s="3">
         <v>3761800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>3757000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>3589500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>3385100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>3554200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>3805100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>3662500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>3660100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>3488800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>3342400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>3423500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>3332800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>3505000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>4256000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>4136200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>4140500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>4392000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>4134200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>4722700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>5483600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>6510500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>7047200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>6942400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>6809800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AD66" s="3">
         <v>7247600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AE66" s="3">
         <v>7134400</v>
       </c>
     </row>
-    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5179,8 +5501,10 @@
       <c r="AA67" s="3"/>
       <c r="AB67" s="3"/>
       <c r="AC67" s="3"/>
-    </row>
-    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD67" s="3"/>
+      <c r="AE67" s="3"/>
+    </row>
+    <row r="68" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5262,8 +5586,14 @@
       <c r="AC68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5345,8 +5675,14 @@
       <c r="AC69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5428,8 +5764,14 @@
       <c r="AC70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5511,91 +5853,103 @@
       <c r="AC71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>391400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>389500</v>
+      </c>
+      <c r="F72" s="3">
         <v>846600</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>845500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>901500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>850100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>1035300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>1108400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>725400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>724900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>948900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>909100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>1197100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>1165400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>1061500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>1129900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>875900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>1144000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>943300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>1280900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>1011600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>943900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>555200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>881800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>4151200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>4823300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AD72" s="3">
         <v>3531600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AE72" s="3">
         <v>4213700</v>
       </c>
     </row>
-    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5677,8 +6031,14 @@
       <c r="AC73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5760,8 +6120,14 @@
       <c r="AC74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5843,91 +6209,103 @@
       <c r="AC75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4435500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>4414300</v>
+      </c>
+      <c r="F76" s="3">
         <v>4909800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>4903600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>4917100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>4637000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>5055300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>5412100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>4797400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>4794300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>5061900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>4849500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>5305600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>5165000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>5303900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>5278400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>5189400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>5351600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>5106300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>5509100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>5441500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>5678800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>5268300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>5350100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>8347700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>8365800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AD76" s="3">
         <v>7108000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AE76" s="3">
         <v>7873100</v>
       </c>
     </row>
-    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6009,179 +6387,197 @@
       <c r="AC77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
+      <c r="AD77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:31" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:31" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>43281</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>43100</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42916</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42735</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42551</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42369</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AD80" s="2">
         <v>42185</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AE80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>98200</v>
+      </c>
+      <c r="E81" s="3">
+        <v>97700</v>
+      </c>
+      <c r="F81" s="3">
         <v>115100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>114900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>112300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>105900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>173400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>185600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>99200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>99100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>122300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>117200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>118200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>115100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>63900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>360900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>59500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>269300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>56000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>488000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>250200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>598600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>-22600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>-2606100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>-285700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1176500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AD81" s="3">
         <v>-104000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AE81" s="3">
         <v>321300</v>
       </c>
     </row>
-    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6211,91 +6607,99 @@
       <c r="AA82" s="3"/>
       <c r="AB82" s="3"/>
       <c r="AC82" s="3"/>
-    </row>
-    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD82" s="3"/>
+      <c r="AE82" s="3"/>
+    </row>
+    <row r="83" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E83" s="3">
+        <v>18100</v>
+      </c>
+      <c r="F83" s="3">
         <v>22500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>24100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>25300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>25300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>37600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>25000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>24100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>23500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>28900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>26700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>25500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>27600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>-28400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>194500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>204700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>206000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>188400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="W83" s="3">
         <v>158600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="X83" s="3">
         <v>163700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="Y83" s="3">
         <v>103300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Z83" s="3">
         <v>206400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="AA83" s="3">
         <v>118200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AB83" s="3">
         <v>237900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AC83" s="3">
         <v>1250800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AD83" s="3">
         <v>219900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AE83" s="3">
         <v>256800</v>
       </c>
     </row>
-    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6377,8 +6781,14 @@
       <c r="AC84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6460,8 +6870,14 @@
       <c r="AC85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6543,8 +6959,14 @@
       <c r="AC86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6626,8 +7048,14 @@
       <c r="AC87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6709,91 +7137,103 @@
       <c r="AC88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>226900</v>
+      </c>
+      <c r="E89" s="3">
+        <v>225800</v>
+      </c>
+      <c r="F89" s="3">
         <v>312200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>311900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>131500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>124000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>345500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>369900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>47400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>47400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>326100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>312400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>8300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>8000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>237400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>680800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-177400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>665100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>-199100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>774600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>-230300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>846200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>-399400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>902800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>-417600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>763000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AD89" s="3">
         <v>-492500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AE89" s="3">
         <v>999400</v>
       </c>
     </row>
-    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6823,91 +7263,99 @@
       <c r="AA90" s="3"/>
       <c r="AB90" s="3"/>
       <c r="AC90" s="3"/>
-    </row>
-    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD90" s="3"/>
+      <c r="AE90" s="3"/>
+    </row>
+    <row r="91" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-17200</v>
+      </c>
+      <c r="F91" s="3">
         <v>-10100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-10100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-9600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-9400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-10100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-11400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-11400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-8900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-8500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-10200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-9900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-56000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-78000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-98000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-45300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-46400</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-42600</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-70800</v>
       </c>
       <c r="X91" s="3">
         <v>-42600</v>
       </c>
       <c r="Y91" s="3">
+        <v>-70800</v>
+      </c>
+      <c r="Z91" s="3">
+        <v>-42600</v>
+      </c>
+      <c r="AA91" s="3">
         <v>-53000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-58200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-65200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AD91" s="3">
         <v>-125100</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AE91" s="3">
         <v>-160600</v>
       </c>
     </row>
-    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6989,8 +7437,14 @@
       <c r="AC92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7072,91 +7526,103 @@
       <c r="AC93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-41800</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-41600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-147400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-147200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-16400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-15500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-31300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-33500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-51200</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-51200</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-36300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-34800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-155000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-150900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>99400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>15400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>718300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-132800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-260000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>113500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>157100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>1016000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-89200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-27100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>1753000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AD94" s="3">
         <v>-15800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AE94" s="3">
         <v>-92200</v>
       </c>
     </row>
-    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7186,91 +7652,99 @@
       <c r="AA95" s="3"/>
       <c r="AB95" s="3"/>
       <c r="AC95" s="3"/>
-    </row>
-    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD95" s="3"/>
+      <c r="AE95" s="3"/>
+    </row>
+    <row r="96" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>71600</v>
+      </c>
+      <c r="E96" s="3">
+        <v>71300</v>
+      </c>
+      <c r="F96" s="3">
         <v>33600</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>33600</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>75400</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>71100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>30700</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>32800</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>67600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>67600</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>30600</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>29300</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>67400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>65600</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>29500</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-57600</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-125300</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-57100</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-120400</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-52500</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-123800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-58000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-368800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-181000</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-358100</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-190400</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AD96" s="3">
         <v>-364800</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AE96" s="3">
         <v>-181700</v>
       </c>
     </row>
-    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -7352,8 +7826,14 @@
       <c r="AC97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -7435,8 +7915,14 @@
       <c r="AC98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7518,253 +8004,277 @@
       <c r="AC99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
+      <c r="AD99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-178500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-177600</v>
+      </c>
+      <c r="F100" s="3">
         <v>-188400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-188200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-225400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-212500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-173400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-185600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>22700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>22700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-317800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-304500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>31100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>30300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-235600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-129200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-245600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-455400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>316000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-557500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-362100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1661300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-778900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-219200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-671000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-811300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AD100" s="3">
         <v>339700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AE100" s="3">
         <v>-809800</v>
       </c>
     </row>
-    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-24000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-22600</v>
+      </c>
+      <c r="F101" s="3">
         <v>-8800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-9400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-4400</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-4400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>3200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-8300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-8000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-10200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-9500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>32200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>34800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-17900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>14900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>-38500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>-2400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-56100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>41000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>-17300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>14800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>89200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>17000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AD101" s="3">
         <v>-42100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AE101" s="3">
         <v>5300</v>
       </c>
     </row>
-    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:31" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="F102" s="3">
         <v>-9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-134300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-126600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>132100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>141400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>14500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>14500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-24800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-23800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-123900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-120600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>91000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>549000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>310200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>38500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>-145500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>274500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-439300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>242000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>-1284800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>673700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>-1026500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>1721700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AD102" s="3">
         <v>-210700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AE102" s="3">
         <v>102700</v>
       </c>
     </row>
